--- a/planning.xlsx
+++ b/planning.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="58">
   <si>
     <t>Planning</t>
   </si>
@@ -173,6 +173,21 @@
   </si>
   <si>
     <t>Tijd om alles nogmaals goed te testen</t>
+  </si>
+  <si>
+    <t>Overleg opdrachtgever 10:00</t>
+  </si>
+  <si>
+    <t>Kickoff 11:15</t>
+  </si>
+  <si>
+    <t>Opdracht omschrijving gekregen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overleg over wat er in de app moeten </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> komen</t>
   </si>
 </sst>
 </file>
@@ -456,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -505,6 +520,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -806,20 +822,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="34.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:21" ht="34.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="1:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>1</v>
       </c>
@@ -843,7 +859,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" s="13">
         <v>41023</v>
       </c>
@@ -853,15 +869,12 @@
       <c r="E3" s="10"/>
       <c r="F3" s="11"/>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="J3" s="11"/>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>5</v>
       </c>
@@ -869,9 +882,7 @@
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
-      <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
@@ -881,7 +892,7 @@
       <c r="N4" s="3"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B5" s="14">
         <v>41026</v>
       </c>
@@ -889,11 +900,13 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
@@ -903,14 +916,14 @@
       <c r="N5" s="3"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="24"/>
       <c r="D6" s="23"/>
       <c r="E6" s="23"/>
       <c r="F6" s="21"/>
       <c r="G6" s="30" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -921,16 +934,14 @@
       <c r="N6" s="3"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
@@ -940,7 +951,7 @@
       <c r="N7" s="3"/>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
       <c r="C8" s="24"/>
       <c r="D8" s="23"/>
@@ -956,13 +967,13 @@
       <c r="N8" s="3"/>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="17" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="4"/>
@@ -976,17 +987,13 @@
       <c r="N9" s="3"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21"/>
-      <c r="G10" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="4"/>
@@ -996,16 +1003,14 @@
       <c r="N10" s="3"/>
       <c r="O10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
       <c r="C11" s="17" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="30" t="s">
-        <v>20</v>
-      </c>
+      <c r="G11" s="30"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="4"/>
@@ -1014,95 +1019,113 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U11" s="36"/>
+    </row>
+    <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="18"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="3"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="26"/>
       <c r="E12" s="20"/>
-      <c r="F12" s="4"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
-      <c r="J12" s="4"/>
+      <c r="J12" s="19"/>
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="25">
-        <v>41029</v>
-      </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="28" t="s">
-        <v>12</v>
+    <row r="13" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="13">
+        <v>41023</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>6</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="29"/>
+      <c r="F13" s="4"/>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" t="s">
-        <v>23</v>
-      </c>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="4"/>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="33">
-        <v>41033</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="19"/>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="13">
-        <v>41036</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="11"/>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
+        <v>41026</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="9"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="3"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
@@ -1113,24 +1136,16 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="14">
-        <v>41040</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="30"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -1138,11 +1153,15 @@
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="9"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="30"/>
+      <c r="C19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="4"/>
@@ -1154,12 +1173,15 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="9"/>
-      <c r="C20" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="3"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
@@ -1171,13 +1193,14 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="9"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="23"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="3"/>
+      <c r="C21" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="30" t="s">
+        <v>20</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
@@ -1187,71 +1210,60 @@
       <c r="N21" s="3"/>
       <c r="O21" s="4"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="9"/>
-      <c r="C22" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="3"/>
+    <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="18"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="9"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="19"/>
+    </row>
+    <row r="23" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="25">
+        <v>41029</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="29"/>
       <c r="O23" s="4"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="9"/>
-      <c r="C24" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="3"/>
+      <c r="B24" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
+      <c r="G24" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="26"/>
+      <c r="B25" s="33">
+        <v>41033</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
       <c r="E25" s="20"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
-      <c r="J25" s="19"/>
+      <c r="J25" s="20"/>
       <c r="K25" s="20"/>
       <c r="L25" s="20"/>
       <c r="M25" s="20"/>
@@ -1260,19 +1272,19 @@
     </row>
     <row r="26" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13">
-        <v>41043</v>
-      </c>
-      <c r="C26" s="16" t="s">
+        <v>41036</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>6</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="31" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="O26" s="4"/>
     </row>
@@ -1284,9 +1296,7 @@
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
@@ -1298,7 +1308,7 @@
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="14">
-        <v>41047</v>
+        <v>41040</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>7</v>
@@ -1312,7 +1322,9 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -1354,7 +1366,9 @@
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="9"/>
       <c r="C31" s="24"/>
-      <c r="D31" s="23"/>
+      <c r="D31" s="23" t="s">
+        <v>28</v>
+      </c>
       <c r="E31" s="23"/>
       <c r="F31" s="21"/>
       <c r="G31" s="3"/>
@@ -1373,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
@@ -1393,7 +1407,9 @@
       <c r="D33" s="22"/>
       <c r="E33" s="23"/>
       <c r="F33" s="21"/>
-      <c r="G33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
@@ -1438,7 +1454,7 @@
     </row>
     <row r="36" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13">
-        <v>41050</v>
+        <v>41043</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>6</v>
@@ -1446,11 +1462,11 @@
       <c r="E36" s="10"/>
       <c r="F36" s="11"/>
       <c r="G36" s="31" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J36" s="11"/>
       <c r="K36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O36" s="4"/>
     </row>
@@ -1462,7 +1478,9 @@
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
       <c r="F37" s="21"/>
-      <c r="G37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
@@ -1474,7 +1492,7 @@
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" s="14">
-        <v>41054</v>
+        <v>41047</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>7</v>
@@ -1515,9 +1533,6 @@
       <c r="C40" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D40" t="s">
-        <v>34</v>
-      </c>
       <c r="E40" s="3"/>
       <c r="F40" s="4"/>
       <c r="G40" s="3"/>
@@ -1552,13 +1567,11 @@
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
@@ -1571,20 +1584,14 @@
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="9"/>
       <c r="C43" s="24"/>
-      <c r="D43" s="22" t="s">
-        <v>38</v>
-      </c>
+      <c r="D43" s="22"/>
       <c r="E43" s="23"/>
       <c r="F43" s="21"/>
-      <c r="G43" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
@@ -1601,9 +1608,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
@@ -1627,20 +1632,20 @@
     </row>
     <row r="46" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B46" s="13">
-        <v>41057</v>
+        <v>41050</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D46" t="s">
-        <v>49</v>
-      </c>
       <c r="E46" s="10"/>
       <c r="F46" s="11"/>
-      <c r="G46" s="3" t="s">
-        <v>41</v>
+      <c r="G46" s="31" t="s">
+        <v>35</v>
       </c>
       <c r="J46" s="11"/>
+      <c r="K46" t="s">
+        <v>36</v>
+      </c>
       <c r="O46" s="4"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
@@ -1663,7 +1668,7 @@
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
-        <v>41061</v>
+        <v>41054</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>7</v>
@@ -1704,6 +1709,9 @@
       <c r="C50" s="17" t="s">
         <v>8</v>
       </c>
+      <c r="D50" t="s">
+        <v>34</v>
+      </c>
       <c r="E50" s="3"/>
       <c r="F50" s="4"/>
       <c r="G50" s="3"/>
@@ -1737,9 +1745,14 @@
       <c r="C52" s="17" t="s">
         <v>9</v>
       </c>
+      <c r="D52" t="s">
+        <v>37</v>
+      </c>
       <c r="E52" s="3"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="3"/>
+      <c r="G52" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
@@ -1752,14 +1765,20 @@
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B53" s="9"/>
       <c r="C53" s="24"/>
-      <c r="D53" s="22"/>
+      <c r="D53" s="22" t="s">
+        <v>38</v>
+      </c>
       <c r="E53" s="23"/>
       <c r="F53" s="21"/>
-      <c r="G53" s="3"/>
+      <c r="G53" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="4"/>
-      <c r="K53" s="3"/>
+      <c r="K53" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
@@ -1776,7 +1795,9 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="4"/>
-      <c r="K54" s="3"/>
+      <c r="K54" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
@@ -1800,23 +1821,20 @@
     </row>
     <row r="56" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B56" s="13">
-        <v>41064</v>
+        <v>41057</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="31" t="s">
-        <v>50</v>
+      <c r="G56" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="J56" s="11"/>
-      <c r="K56" t="s">
-        <v>46</v>
-      </c>
       <c r="O56" s="4"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
@@ -1831,17 +1849,15 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="4"/>
-      <c r="K57" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" s="4"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B58" s="14" t="s">
-        <v>44</v>
+      <c r="B58" s="14">
+        <v>41061</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>7</v>
@@ -1961,60 +1977,238 @@
       <c r="O64" s="4"/>
     </row>
     <row r="65" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="4"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="19"/>
     </row>
     <row r="66" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="35">
+      <c r="B66" s="13">
+        <v>41064</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="10"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="J66" s="11"/>
+      <c r="K66" t="s">
+        <v>46</v>
+      </c>
+      <c r="O66" s="4"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B67" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="24"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B68" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="4"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B69" s="9"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B70" s="9"/>
+      <c r="C70" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B71" s="9"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B72" s="9"/>
+      <c r="C72" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B73" s="9"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B74" s="9"/>
+      <c r="C74" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="3"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="35">
         <v>41071</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C76" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
-      <c r="N66" s="29"/>
-      <c r="O66" s="32"/>
-    </row>
-    <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="18" t="s">
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="29"/>
+      <c r="M76" s="29"/>
+      <c r="N76" s="29"/>
+      <c r="O76" s="32"/>
+    </row>
+    <row r="77" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
-      <c r="K67" s="20"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="20"/>
-      <c r="N67" s="20"/>
-      <c r="O67" s="19"/>
-    </row>
-    <row r="68" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="20"/>
+      <c r="L77" s="20"/>
+      <c r="M77" s="20"/>
+      <c r="N77" s="20"/>
+      <c r="O77" s="19"/>
+    </row>
+    <row r="78" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="90" windowWidth="12435" windowHeight="5190"/>
+    <workbookView xWindow="360" yWindow="90" windowWidth="12435" windowHeight="5190" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="Blad2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="70">
   <si>
     <t>Planning</t>
   </si>
@@ -188,13 +189,61 @@
   </si>
   <si>
     <t xml:space="preserve"> komen</t>
+  </si>
+  <si>
+    <t>Planning schema</t>
+  </si>
+  <si>
+    <t>Taak</t>
+  </si>
+  <si>
+    <t>Tijd in weken</t>
+  </si>
+  <si>
+    <t>Onderzoek</t>
+  </si>
+  <si>
+    <t>Ontwikkelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "framework"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ontwikkelen </t>
+  </si>
+  <si>
+    <t>Testing + degugging</t>
+  </si>
+  <si>
+    <t>Uitloop</t>
+  </si>
+  <si>
+    <t>Raport</t>
+  </si>
+  <si>
+    <t>Acceptatie test</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>opdrachtgevers</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,16 +266,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -467,11 +529,498 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -521,6 +1070,70 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -2213,4 +2826,588 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N78"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="6" width="5" customWidth="1"/>
+    <col min="10" max="11" width="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="93" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="91"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="100" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="50"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="59">
+        <v>1</v>
+      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="76">
+        <v>2</v>
+      </c>
+      <c r="G4" s="78">
+        <v>3</v>
+      </c>
+      <c r="H4" s="78">
+        <v>4</v>
+      </c>
+      <c r="I4" s="78">
+        <v>5</v>
+      </c>
+      <c r="J4" s="20"/>
+      <c r="K4" s="76">
+        <v>6</v>
+      </c>
+      <c r="L4" s="78">
+        <v>7</v>
+      </c>
+      <c r="M4" s="78">
+        <v>8</v>
+      </c>
+      <c r="N4" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="94" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="49"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="52"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="44"/>
+      <c r="D6" s="61"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="52"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="61"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="82"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="95" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="51"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="96" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="48"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="53"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="97" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="52"/>
+    </row>
+    <row r="12" spans="1:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="54"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="44"/>
+      <c r="D13" s="61"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="80"/>
+      <c r="N13" s="55"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="92" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="57"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>